--- a/samples/예시데이터_ContactList.xlsx
+++ b/samples/예시데이터_ContactList.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -529,9 +529,35 @@
         <v/>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>EX-E05</v>
+      </c>
+      <c r="B6" t="str">
+        <v>Echo Lighting Inc. (예시)</v>
+      </c>
+      <c r="C6" t="str">
+        <v>Emma Stone</v>
+      </c>
+      <c r="D6" t="str">
+        <v>emma.stone@echo-group.example.com</v>
+      </c>
+      <c r="E6" t="str">
+        <v>orders@echo-group.example.com</v>
+      </c>
+      <c r="F6" t="str">
+        <v>+1-000-000-0005</v>
+      </c>
+      <c r="G6" t="str">
+        <v>USA</v>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H5"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
   </ignoredErrors>
 </worksheet>
 </file>